--- a/tabela_adapta_brasi.xlsx
+++ b/tabela_adapta_brasi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albertodiniz/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17CBBAA4-EA84-DE46-8FB2-6B58875CBDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95ECC56-5C8D-404E-A055-525E0744A574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="16900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General_Data_Base" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12563" uniqueCount="2083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12562" uniqueCount="2082">
   <si>
     <t>indicator_id</t>
   </si>
@@ -6276,9 +6276,6 @@
   </si>
   <si>
     <t>Indicador simples climático que compõe o indicador temático resiliência climática. Este indicador busca predizer a relação dos biomas terrestres com o clima dominante. O cálculo desse indicador foi obtido a partir do valor médio de amplitude anual de temperatura no município. O dado de amplitude anual de temperatura foi obtido em Pinho et al. (2020) disponibilizado pela Quarta Comunicação Nacional do Brasil à Convenção do Clima das Nações Unidas, sendo que os autores adotaram a variável amplitude anual de temperatura a partir do Modelo Regional ETA, sob as condições de contorno do modelo global HadGEM2 ES (EtaHadGEM2 ES), desenvolvido pelo Inpe (CHOU et al., 2014) com resolução espacial de 0.20° (24 km) abrangendo toda a América do Sul.Fonte:Sistema de Informações e Análises sobre Impactos das Mudanças Climáticas - AdaptaBrasil MCTI.</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
 </sst>
 </file>
@@ -6642,7 +6639,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y559"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6748,7 +6744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1777</v>
       </c>
@@ -6795,7 +6791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1434</v>
       </c>
@@ -6842,7 +6838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -6889,7 +6885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1667</v>
       </c>
@@ -6936,7 +6932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -6983,7 +6979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1470</v>
       </c>
@@ -7030,7 +7026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>1562</v>
       </c>
@@ -7077,7 +7073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1103</v>
       </c>
@@ -7124,7 +7120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1857</v>
       </c>
@@ -7171,7 +7167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>1956</v>
       </c>
@@ -7218,7 +7214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>1735</v>
       </c>
@@ -7265,7 +7261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1801</v>
       </c>
@@ -7312,7 +7308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1223</v>
       </c>
@@ -7359,7 +7355,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1320</v>
       </c>
@@ -7406,7 +7402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1991</v>
       </c>
@@ -7453,7 +7449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>194</v>
       </c>
@@ -7500,7 +7496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1108</v>
       </c>
@@ -7547,7 +7543,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>369</v>
       </c>
@@ -7594,7 +7590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>379</v>
       </c>
@@ -7641,7 +7637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>259</v>
       </c>
@@ -7688,7 +7684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>270</v>
       </c>
@@ -7735,7 +7731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>280</v>
       </c>
@@ -7782,7 +7778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>305</v>
       </c>
@@ -7829,7 +7825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>314</v>
       </c>
@@ -7876,7 +7872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>323</v>
       </c>
@@ -7923,7 +7919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>332</v>
       </c>
@@ -7970,7 +7966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>341</v>
       </c>
@@ -8017,7 +8013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>350</v>
       </c>
@@ -8064,7 +8060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>359</v>
       </c>
@@ -8111,7 +8107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>390</v>
       </c>
@@ -8158,7 +8154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>398</v>
       </c>
@@ -8205,7 +8201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>406</v>
       </c>
@@ -8252,7 +8248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>415</v>
       </c>
@@ -8299,7 +8295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>424</v>
       </c>
@@ -8346,7 +8342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>433</v>
       </c>
@@ -8393,7 +8389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>440</v>
       </c>
@@ -8440,7 +8436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>449</v>
       </c>
@@ -8487,7 +8483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>458</v>
       </c>
@@ -8534,7 +8530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>246</v>
       </c>
@@ -8581,7 +8577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>2077</v>
       </c>
@@ -8628,7 +8624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>1811</v>
       </c>
@@ -8675,7 +8671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>178</v>
       </c>
@@ -8722,7 +8718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>1330</v>
       </c>
@@ -8769,7 +8765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>2058</v>
       </c>
@@ -8816,7 +8812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>1325</v>
       </c>
@@ -8863,7 +8859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>2054</v>
       </c>
@@ -8910,7 +8906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>1228</v>
       </c>
@@ -8957,7 +8953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>1233</v>
       </c>
@@ -9004,7 +9000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>1079</v>
       </c>
@@ -9051,7 +9047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>1074</v>
       </c>
@@ -9098,7 +9094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>773</v>
       </c>
@@ -9145,7 +9141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>758</v>
       </c>
@@ -9192,7 +9188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>746</v>
       </c>
@@ -9239,7 +9235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>1675</v>
       </c>
@@ -9286,7 +9282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>1733</v>
       </c>
@@ -9333,7 +9329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>1764</v>
       </c>
@@ -9380,7 +9376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>1282</v>
       </c>
@@ -9427,7 +9423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>1429</v>
       </c>
@@ -9474,7 +9470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>158</v>
       </c>
@@ -9521,7 +9517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>825</v>
       </c>
@@ -9568,7 +9564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>696</v>
       </c>
@@ -9615,7 +9611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>1054</v>
       </c>
@@ -9662,7 +9658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>1059</v>
       </c>
@@ -9709,7 +9705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>112</v>
       </c>
@@ -9771,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>656</v>
       </c>
@@ -9818,7 +9814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>674</v>
       </c>
@@ -9865,7 +9861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>679</v>
       </c>
@@ -9912,7 +9908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>466</v>
       </c>
@@ -9959,7 +9955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>475</v>
       </c>
@@ -10006,7 +10002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>481</v>
       </c>
@@ -10053,7 +10049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>487</v>
       </c>
@@ -10100,7 +10096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>493</v>
       </c>
@@ -10147,7 +10143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>499</v>
       </c>
@@ -10194,7 +10190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>505</v>
       </c>
@@ -10241,7 +10237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>511</v>
       </c>
@@ -10288,7 +10284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>517</v>
       </c>
@@ -10335,7 +10331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>523</v>
       </c>
@@ -10382,7 +10378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>529</v>
       </c>
@@ -10429,7 +10425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>532</v>
       </c>
@@ -10476,7 +10472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>538</v>
       </c>
@@ -10523,7 +10519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>688</v>
       </c>
@@ -10570,7 +10566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>1295</v>
       </c>
@@ -10617,7 +10613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>725</v>
       </c>
@@ -10664,7 +10660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>963</v>
       </c>
@@ -10711,7 +10707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>996</v>
       </c>
@@ -10758,7 +10754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>798</v>
       </c>
@@ -10805,7 +10801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>730</v>
       </c>
@@ -10852,7 +10848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>558</v>
       </c>
@@ -10899,7 +10895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>595</v>
       </c>
@@ -10946,7 +10942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>611</v>
       </c>
@@ -10993,7 +10989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>626</v>
       </c>
@@ -11040,7 +11036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>647</v>
       </c>
@@ -11087,7 +11083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>661</v>
       </c>
@@ -11134,7 +11130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>675</v>
       </c>
@@ -11181,7 +11177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>680</v>
       </c>
@@ -11228,7 +11224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>578</v>
       </c>
@@ -11275,7 +11271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>601</v>
       </c>
@@ -11322,7 +11318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>615</v>
       </c>
@@ -11369,7 +11365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>671</v>
       </c>
@@ -11416,7 +11412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>677</v>
       </c>
@@ -11463,7 +11459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>852</v>
       </c>
@@ -11510,7 +11506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>1744</v>
       </c>
@@ -11557,7 +11553,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>1662</v>
       </c>
@@ -11604,7 +11600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>1729</v>
       </c>
@@ -11651,7 +11647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>1760</v>
       </c>
@@ -11698,7 +11694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>1793</v>
       </c>
@@ -11745,7 +11741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>1267</v>
       </c>
@@ -11792,7 +11788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>1257</v>
       </c>
@@ -11839,7 +11835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>1272</v>
       </c>
@@ -11886,7 +11882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>1016</v>
       </c>
@@ -11933,7 +11929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>1033</v>
       </c>
@@ -11980,7 +11976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>2050</v>
       </c>
@@ -12027,7 +12023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>1739</v>
       </c>
@@ -12074,7 +12070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>1766</v>
       </c>
@@ -12121,7 +12117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>1495</v>
       </c>
@@ -12168,7 +12164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>1569</v>
       </c>
@@ -12215,7 +12211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>1608</v>
       </c>
@@ -12262,7 +12258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>2045</v>
       </c>
@@ -12309,7 +12305,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>1465</v>
       </c>
@@ -12356,7 +12352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>1560</v>
       </c>
@@ -12403,7 +12399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>1602</v>
       </c>
@@ -12450,7 +12446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>816</v>
       </c>
@@ -12497,7 +12493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>1050</v>
       </c>
@@ -12544,7 +12540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>1695</v>
       </c>
@@ -12591,7 +12587,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>1805</v>
       </c>
@@ -12638,7 +12634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>1238</v>
       </c>
@@ -12685,7 +12681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>295</v>
       </c>
@@ -12732,7 +12728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>869</v>
       </c>
@@ -12779,7 +12775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>1020</v>
       </c>
@@ -12826,7 +12822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>1936</v>
       </c>
@@ -12873,7 +12869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>1989</v>
       </c>
@@ -12920,7 +12916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>1340</v>
       </c>
@@ -12967,7 +12963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>1671</v>
       </c>
@@ -13014,7 +13010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>1731</v>
       </c>
@@ -13061,7 +13057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>1762</v>
       </c>
@@ -13108,7 +13104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>1799</v>
       </c>
@@ -13155,7 +13151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>992</v>
       </c>
@@ -13202,7 +13198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>1011</v>
       </c>
@@ -13249,7 +13245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>857</v>
       </c>
@@ -13296,7 +13292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>955</v>
       </c>
@@ -13343,7 +13339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>1165</v>
       </c>
@@ -13390,7 +13386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>1447</v>
       </c>
@@ -13437,7 +13433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>1796</v>
       </c>
@@ -13484,7 +13480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>768</v>
       </c>
@@ -13531,7 +13527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>1367</v>
       </c>
@@ -13578,7 +13574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>82</v>
       </c>
@@ -13640,7 +13636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>1685</v>
       </c>
@@ -13687,7 +13683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>1803</v>
       </c>
@@ -13734,7 +13730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>1904</v>
       </c>
@@ -13781,7 +13777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>1978</v>
       </c>
@@ -13828,7 +13824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>200</v>
       </c>
@@ -13875,7 +13871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>220</v>
       </c>
@@ -13922,7 +13918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>183</v>
       </c>
@@ -13969,7 +13965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>1392</v>
       </c>
@@ -14016,7 +14012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>573</v>
       </c>
@@ -14063,7 +14059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>598</v>
       </c>
@@ -14110,7 +14106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>614</v>
       </c>
@@ -14157,7 +14153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>669</v>
       </c>
@@ -14204,7 +14200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>583</v>
       </c>
@@ -14251,7 +14247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>604</v>
       </c>
@@ -14298,7 +14294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>672</v>
       </c>
@@ -14345,7 +14341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>630</v>
       </c>
@@ -14392,7 +14388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>651</v>
       </c>
@@ -14439,7 +14435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>683</v>
       </c>
@@ -14486,7 +14482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>1344</v>
       </c>
@@ -14533,7 +14529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>640</v>
       </c>
@@ -14580,7 +14576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>1520</v>
       </c>
@@ -14627,7 +14623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>1578</v>
       </c>
@@ -14674,7 +14670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>1616</v>
       </c>
@@ -14721,7 +14717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>143</v>
       </c>
@@ -14768,7 +14764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>126</v>
       </c>
@@ -14815,7 +14811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>1300</v>
       </c>
@@ -14862,7 +14858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>1305</v>
       </c>
@@ -14909,7 +14905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>839</v>
       </c>
@@ -14956,7 +14952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>1064</v>
       </c>
@@ -15003,7 +14999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>1442</v>
       </c>
@@ -15050,7 +15046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>1932</v>
       </c>
@@ -15097,7 +15093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>1987</v>
       </c>
@@ -15144,7 +15140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>1909</v>
       </c>
@@ -15191,7 +15187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>1979</v>
       </c>
@@ -15238,7 +15234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>1715</v>
       </c>
@@ -15285,7 +15281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>1751</v>
       </c>
@@ -15332,7 +15328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>1775</v>
       </c>
@@ -15379,7 +15375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>1927</v>
       </c>
@@ -15426,7 +15422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>1986</v>
       </c>
@@ -15473,7 +15469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>635</v>
       </c>
@@ -15520,7 +15516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>650</v>
       </c>
@@ -15567,7 +15563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>682</v>
       </c>
@@ -15614,7 +15610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>701</v>
       </c>
@@ -15661,7 +15657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>1831</v>
       </c>
@@ -15708,7 +15704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>1944</v>
       </c>
@@ -15755,7 +15751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>834</v>
       </c>
@@ -15802,7 +15798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>205</v>
       </c>
@@ -15849,7 +15845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>223</v>
       </c>
@@ -15896,7 +15892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>2030</v>
       </c>
@@ -15943,7 +15939,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1335</v>
       </c>
@@ -15990,7 +15986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>1377</v>
       </c>
@@ -16037,7 +16033,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>1887</v>
       </c>
@@ -16084,7 +16080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>1971</v>
       </c>
@@ -16131,7 +16127,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1291</v>
       </c>
@@ -16178,7 +16174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>778</v>
       </c>
@@ -16225,7 +16221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1475</v>
       </c>
@@ -16272,7 +16268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>1564</v>
       </c>
@@ -16319,7 +16315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>241</v>
       </c>
@@ -16366,7 +16362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>255</v>
       </c>
@@ -16413,7 +16409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>267</v>
       </c>
@@ -16460,7 +16456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>277</v>
       </c>
@@ -16507,7 +16503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>302</v>
       </c>
@@ -16554,7 +16550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>311</v>
       </c>
@@ -16601,7 +16597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>320</v>
       </c>
@@ -16648,7 +16644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>329</v>
       </c>
@@ -16695,7 +16691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>338</v>
       </c>
@@ -16742,7 +16738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>347</v>
       </c>
@@ -16789,7 +16785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>356</v>
       </c>
@@ -16836,7 +16832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>366</v>
       </c>
@@ -16883,7 +16879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>377</v>
       </c>
@@ -16930,7 +16926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>387</v>
       </c>
@@ -16977,7 +16973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>396</v>
       </c>
@@ -17024,7 +17020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>404</v>
       </c>
@@ -17071,7 +17067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>412</v>
       </c>
@@ -17118,7 +17114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>421</v>
       </c>
@@ -17165,7 +17161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>430</v>
       </c>
@@ -17212,7 +17208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>438</v>
       </c>
@@ -17259,7 +17255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>445</v>
       </c>
@@ -17306,7 +17302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>455</v>
       </c>
@@ -17353,7 +17349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1914</v>
       </c>
@@ -17400,7 +17396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1981</v>
       </c>
@@ -17447,7 +17443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>620</v>
       </c>
@@ -17494,7 +17490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>1218</v>
       </c>
@@ -17541,7 +17537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>2006</v>
       </c>
@@ -17588,7 +17584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>1425</v>
       </c>
@@ -17635,7 +17631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>830</v>
       </c>
@@ -17682,7 +17678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>1852</v>
       </c>
@@ -17729,7 +17725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>1952</v>
       </c>
@@ -17776,7 +17772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>1848</v>
       </c>
@@ -17823,7 +17819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>1951</v>
       </c>
@@ -17870,7 +17866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>998</v>
       </c>
@@ -17917,7 +17913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>968</v>
       </c>
@@ -17964,7 +17960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>710</v>
       </c>
@@ -18011,7 +18007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>1826</v>
       </c>
@@ -18058,7 +18054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>1943</v>
       </c>
@@ -18105,7 +18101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>1879</v>
       </c>
@@ -18152,7 +18148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>1969</v>
       </c>
@@ -18199,7 +18195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1875</v>
       </c>
@@ -18246,7 +18242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1968</v>
       </c>
@@ -18293,7 +18289,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>1883</v>
       </c>
@@ -18340,7 +18336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>1970</v>
       </c>
@@ -18387,7 +18383,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>2037</v>
       </c>
@@ -18434,7 +18430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>1208</v>
       </c>
@@ -18481,7 +18477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>548</v>
       </c>
@@ -18528,7 +18524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>592</v>
       </c>
@@ -18575,7 +18571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>609</v>
       </c>
@@ -18622,7 +18618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>624</v>
       </c>
@@ -18669,7 +18665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>645</v>
       </c>
@@ -18716,7 +18712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>1637</v>
       </c>
@@ -18763,7 +18759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>1720</v>
       </c>
@@ -18810,7 +18806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>1753</v>
       </c>
@@ -18857,7 +18853,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>1787</v>
       </c>
@@ -18904,7 +18900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>1438</v>
       </c>
@@ -18951,7 +18947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>1647</v>
       </c>
@@ -18998,7 +18994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>1722</v>
       </c>
@@ -19045,7 +19041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>1918</v>
       </c>
@@ -19092,7 +19088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>1983</v>
       </c>
@@ -19139,7 +19135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>1724</v>
       </c>
@@ -19186,7 +19182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>1755</v>
       </c>
@@ -19233,7 +19229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1789</v>
       </c>
@@ -19280,7 +19276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>616</v>
       </c>
@@ -19327,7 +19323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>678</v>
       </c>
@@ -19374,7 +19370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>1348</v>
       </c>
@@ -19421,7 +19417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>861</v>
       </c>
@@ -19468,7 +19464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>1046</v>
       </c>
@@ -19515,7 +19511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>1042</v>
       </c>
@@ -19562,7 +19558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>983</v>
       </c>
@@ -19609,7 +19605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1007</v>
       </c>
@@ -19656,7 +19652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>1025</v>
       </c>
@@ -19703,7 +19699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>787</v>
       </c>
@@ -19750,7 +19746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>102</v>
       </c>
@@ -19812,7 +19808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>63</v>
       </c>
@@ -19874,7 +19870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>91</v>
       </c>
@@ -19930,7 +19926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1387</v>
       </c>
@@ -19977,7 +19973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>691</v>
       </c>
@@ -20024,7 +20020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>1843</v>
       </c>
@@ -20071,7 +20067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>1948</v>
       </c>
@@ -20118,7 +20114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>1410</v>
       </c>
@@ -20165,7 +20161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>750</v>
       </c>
@@ -20212,7 +20208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>795</v>
       </c>
@@ -20259,7 +20255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>1028</v>
       </c>
@@ -20306,7 +20302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>229</v>
       </c>
@@ -20353,7 +20349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>821</v>
       </c>
@@ -20400,7 +20396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>1705</v>
       </c>
@@ -20447,7 +20443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>1749</v>
       </c>
@@ -20494,7 +20490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>1773</v>
       </c>
@@ -20541,7 +20537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>1810</v>
       </c>
@@ -20588,7 +20584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>811</v>
       </c>
@@ -20635,7 +20631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>189</v>
       </c>
@@ -20682,7 +20678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>1248</v>
       </c>
@@ -20729,7 +20725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>1822</v>
       </c>
@@ -20776,7 +20772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>1941</v>
       </c>
@@ -20823,7 +20819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>1405</v>
       </c>
@@ -20870,7 +20866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>1117</v>
       </c>
@@ -20917,7 +20913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>1112</v>
       </c>
@@ -20964,7 +20960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>1652</v>
       </c>
@@ -21011,7 +21007,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>1899</v>
       </c>
@@ -21058,7 +21054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>1976</v>
       </c>
@@ -21105,7 +21101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>168</v>
       </c>
@@ -21152,7 +21148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>173</v>
       </c>
@@ -21199,7 +21195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1358</v>
       </c>
@@ -21246,7 +21242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>163</v>
       </c>
@@ -21293,7 +21289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1657</v>
       </c>
@@ -21340,7 +21336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>904</v>
       </c>
@@ -21387,7 +21383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>926</v>
       </c>
@@ -21434,7 +21430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>941</v>
       </c>
@@ -21481,7 +21477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>958</v>
       </c>
@@ -21528,7 +21524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>2034</v>
       </c>
@@ -21575,7 +21571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1353</v>
       </c>
@@ -21622,7 +21618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>870</v>
       </c>
@@ -21669,7 +21665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>878</v>
       </c>
@@ -21716,7 +21712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>874</v>
       </c>
@@ -21763,7 +21759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>881</v>
       </c>
@@ -21810,7 +21806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>884</v>
       </c>
@@ -21857,7 +21853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>1680</v>
       </c>
@@ -21904,7 +21900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>2025</v>
       </c>
@@ -21951,7 +21947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>891</v>
       </c>
@@ -21998,7 +21994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>916</v>
       </c>
@@ -22045,7 +22041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>1584</v>
       </c>
@@ -22092,7 +22088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>1500</v>
       </c>
@@ -22139,7 +22135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>1571</v>
       </c>
@@ -22186,7 +22182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>1610</v>
       </c>
@@ -22233,7 +22229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>988</v>
       </c>
@@ -22280,7 +22276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>1008</v>
       </c>
@@ -22327,7 +22323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>1540</v>
       </c>
@@ -22374,7 +22370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1592</v>
       </c>
@@ -22421,7 +22417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1625</v>
       </c>
@@ -22468,7 +22464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1012</v>
       </c>
@@ -22515,7 +22511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1382</v>
       </c>
@@ -22562,7 +22558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>1099</v>
       </c>
@@ -22609,7 +22605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1535</v>
       </c>
@@ -22656,7 +22652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1589</v>
       </c>
@@ -22703,7 +22699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>1622</v>
       </c>
@@ -22750,7 +22746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>563</v>
       </c>
@@ -22797,7 +22793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>596</v>
       </c>
@@ -22844,7 +22840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>612</v>
       </c>
@@ -22891,7 +22887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>627</v>
       </c>
@@ -22938,7 +22934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>648</v>
       </c>
@@ -22985,7 +22981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>1397</v>
       </c>
@@ -23032,7 +23028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>1816</v>
       </c>
@@ -23079,7 +23075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>1525</v>
       </c>
@@ -23126,7 +23122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>1580</v>
       </c>
@@ -23173,7 +23169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>1618</v>
       </c>
@@ -23220,7 +23216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>1277</v>
       </c>
@@ -23267,7 +23263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>2042</v>
       </c>
@@ -23314,7 +23310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>1146</v>
       </c>
@@ -23361,7 +23357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>1151</v>
       </c>
@@ -23408,7 +23404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>2011</v>
       </c>
@@ -23455,7 +23451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>2020</v>
       </c>
@@ -23502,7 +23498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>1549</v>
       </c>
@@ -23549,7 +23545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>2015</v>
       </c>
@@ -23596,7 +23592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1243</v>
       </c>
@@ -23643,7 +23639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>783</v>
       </c>
@@ -23690,7 +23686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>919</v>
       </c>
@@ -23737,7 +23733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>934</v>
       </c>
@@ -23784,7 +23780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>895</v>
       </c>
@@ -23831,7 +23827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>949</v>
       </c>
@@ -23878,7 +23874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>843</v>
       </c>
@@ -23925,7 +23921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1515</v>
       </c>
@@ -23972,7 +23968,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1576</v>
       </c>
@@ -24019,7 +24015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1615</v>
       </c>
@@ -24066,7 +24062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>715</v>
       </c>
@@ -24113,7 +24109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1866</v>
       </c>
@@ -24160,7 +24156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1963</v>
       </c>
@@ -24207,7 +24203,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1510</v>
       </c>
@@ -24254,7 +24250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1574</v>
       </c>
@@ -24301,7 +24297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1613</v>
       </c>
@@ -24348,7 +24344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1094</v>
       </c>
@@ -24395,7 +24391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1892</v>
       </c>
@@ -24442,7 +24438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1972</v>
       </c>
@@ -24489,7 +24485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1490</v>
       </c>
@@ -24536,7 +24532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>1568</v>
       </c>
@@ -24583,7 +24579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1606</v>
       </c>
@@ -24630,7 +24626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>806</v>
       </c>
@@ -24677,7 +24673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>973</v>
       </c>
@@ -24724,7 +24720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>1003</v>
       </c>
@@ -24771,7 +24767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>978</v>
       </c>
@@ -24818,7 +24814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1004</v>
       </c>
@@ -24865,7 +24861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>2028</v>
       </c>
@@ -24912,7 +24908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1894</v>
       </c>
@@ -24959,7 +24955,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>1973</v>
       </c>
@@ -25006,7 +25002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1363</v>
       </c>
@@ -25053,7 +25049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>734</v>
       </c>
@@ -25100,7 +25096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>803</v>
       </c>
@@ -25147,7 +25143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1690</v>
       </c>
@@ -25194,7 +25190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1451</v>
       </c>
@@ -25241,7 +25237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1141</v>
       </c>
@@ -25288,7 +25284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>291</v>
       </c>
@@ -25335,7 +25331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>868</v>
       </c>
@@ -25382,7 +25378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>283</v>
       </c>
@@ -25429,7 +25425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>866</v>
       </c>
@@ -25476,7 +25472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>287</v>
       </c>
@@ -25523,7 +25519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>867</v>
       </c>
@@ -25570,7 +25566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1315</v>
       </c>
@@ -25617,7 +25613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>742</v>
       </c>
@@ -25664,7 +25660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>2063</v>
       </c>
@@ -25711,7 +25707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>1544</v>
       </c>
@@ -25758,7 +25754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>1782</v>
       </c>
@@ -25805,7 +25801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>705</v>
       </c>
@@ -25852,7 +25848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1836</v>
       </c>
@@ -25899,7 +25895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1945</v>
       </c>
@@ -25946,7 +25942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1122</v>
       </c>
@@ -25993,7 +25989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1840</v>
       </c>
@@ -26040,7 +26036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1946</v>
       </c>
@@ -26087,7 +26083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1262</v>
       </c>
@@ -26134,7 +26130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1126</v>
       </c>
@@ -26181,7 +26177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1420</v>
       </c>
@@ -26228,7 +26224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>1252</v>
       </c>
@@ -26275,7 +26271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1415</v>
       </c>
@@ -26322,7 +26318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1287</v>
       </c>
@@ -26369,7 +26365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>1069</v>
       </c>
@@ -26416,7 +26412,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1372</v>
       </c>
@@ -26463,7 +26459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>210</v>
       </c>
@@ -26510,7 +26506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>34</v>
       </c>
@@ -26566,7 +26562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>754</v>
       </c>
@@ -26613,7 +26609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1485</v>
       </c>
@@ -26660,7 +26656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>1566</v>
       </c>
@@ -26707,7 +26703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>1604</v>
       </c>
@@ -26754,7 +26750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1156</v>
       </c>
@@ -26801,7 +26797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>847</v>
       </c>
@@ -26848,7 +26844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1161</v>
       </c>
@@ -26895,7 +26891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>1136</v>
       </c>
@@ -26942,7 +26938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1131</v>
       </c>
@@ -26989,7 +26985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1038</v>
       </c>
@@ -27036,7 +27032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>720</v>
       </c>
@@ -27083,7 +27079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1505</v>
       </c>
@@ -27130,7 +27126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>1573</v>
       </c>
@@ -27177,7 +27173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1612</v>
       </c>
@@ -27265,7 +27261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1627</v>
       </c>
@@ -27312,7 +27308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>120</v>
       </c>
@@ -27359,7 +27355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>553</v>
       </c>
@@ -27406,7 +27402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>594</v>
       </c>
@@ -27453,7 +27449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>610</v>
       </c>
@@ -27500,7 +27496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>625</v>
       </c>
@@ -27547,7 +27543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>646</v>
       </c>
@@ -27594,7 +27590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1922</v>
       </c>
@@ -27641,7 +27637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1984</v>
       </c>
@@ -27688,7 +27684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>74</v>
       </c>
@@ -27750,7 +27746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>791</v>
       </c>
@@ -27797,7 +27793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>2068</v>
       </c>
@@ -27844,7 +27840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>44</v>
       </c>
@@ -27906,7 +27902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1089</v>
       </c>
@@ -27953,7 +27949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>54</v>
       </c>
@@ -28015,7 +28011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1530</v>
       </c>
@@ -28062,7 +28058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1582</v>
       </c>
@@ -28109,7 +28105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1620</v>
       </c>
@@ -28156,7 +28152,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1632</v>
       </c>
@@ -28203,7 +28199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1996</v>
       </c>
@@ -28250,7 +28246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>2001</v>
       </c>
@@ -28297,7 +28293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>461</v>
       </c>
@@ -28344,7 +28340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>471</v>
       </c>
@@ -28391,7 +28387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>478</v>
       </c>
@@ -28438,7 +28434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>484</v>
       </c>
@@ -28485,7 +28481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>490</v>
       </c>
@@ -28532,7 +28528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>496</v>
       </c>
@@ -28579,7 +28575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>502</v>
       </c>
@@ -28626,7 +28622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>508</v>
       </c>
@@ -28673,7 +28669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>514</v>
       </c>
@@ -28720,7 +28716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>520</v>
       </c>
@@ -28767,7 +28763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>526</v>
       </c>
@@ -28814,7 +28810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>535</v>
       </c>
@@ -28861,7 +28857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>541</v>
       </c>
@@ -28908,7 +28904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>685</v>
       </c>
@@ -28955,7 +28951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>899</v>
       </c>
@@ -29002,7 +28998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>924</v>
       </c>
@@ -29049,7 +29045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>939</v>
       </c>
@@ -29096,7 +29092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>953</v>
       </c>
@@ -29143,7 +29139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1480</v>
       </c>
@@ -29190,7 +29186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1861</v>
       </c>
@@ -29237,7 +29233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1959</v>
       </c>
@@ -29284,7 +29280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1400</v>
       </c>
@@ -29331,7 +29327,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1213</v>
       </c>
@@ -29378,7 +29374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1199</v>
       </c>
@@ -29425,7 +29421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1204</v>
       </c>
@@ -29472,7 +29468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>588</v>
       </c>
@@ -29519,7 +29515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>654</v>
       </c>
@@ -29566,7 +29562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>605</v>
       </c>
@@ -29613,7 +29609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>673</v>
       </c>
@@ -29660,7 +29656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>887</v>
       </c>
@@ -29707,7 +29703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>913</v>
       </c>
@@ -29754,7 +29750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>931</v>
       </c>
@@ -29801,7 +29797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>946</v>
       </c>
@@ -29848,7 +29844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>215</v>
       </c>
@@ -29895,7 +29891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>226</v>
       </c>
@@ -29942,7 +29938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>2072</v>
       </c>
@@ -29989,7 +29985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1700</v>
       </c>
@@ -30036,7 +30032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1748</v>
       </c>
@@ -30083,7 +30079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1807</v>
       </c>
@@ -30130,7 +30126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1768</v>
       </c>
@@ -30177,7 +30173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1809</v>
       </c>
@@ -30224,7 +30220,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>148</v>
       </c>
@@ -30271,7 +30267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1460</v>
       </c>
@@ -30318,7 +30314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1557</v>
       </c>
@@ -30365,7 +30361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1456</v>
       </c>
@@ -30412,7 +30408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>1554</v>
       </c>
@@ -30459,7 +30455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>1599</v>
       </c>
@@ -30506,7 +30502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>1310</v>
       </c>
@@ -30553,7 +30549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>1642</v>
       </c>
@@ -30600,7 +30596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>1710</v>
       </c>
@@ -30647,7 +30643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>1750</v>
       </c>
@@ -30694,7 +30690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1774</v>
       </c>
@@ -30741,7 +30737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>1821</v>
       </c>
@@ -30788,7 +30784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>908</v>
       </c>
@@ -30835,7 +30831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>928</v>
       </c>
@@ -30882,7 +30878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>943</v>
       </c>
@@ -30929,7 +30925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>960</v>
       </c>
@@ -30976,7 +30972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>1871</v>
       </c>
@@ -31023,7 +31019,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>1967</v>
       </c>
@@ -31070,7 +31066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>1190</v>
       </c>
@@ -31117,7 +31113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>1195</v>
       </c>
@@ -31164,7 +31160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>1182</v>
       </c>
@@ -31211,7 +31207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>1186</v>
       </c>
@@ -31258,7 +31254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>738</v>
       </c>
@@ -31305,7 +31301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>1178</v>
       </c>
@@ -31352,7 +31348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>1173</v>
       </c>
@@ -31399,7 +31395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>1168</v>
       </c>
@@ -31446,7 +31442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>1084</v>
       </c>
@@ -31493,7 +31489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>664</v>
       </c>
@@ -31540,7 +31536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>676</v>
       </c>
@@ -31587,7 +31583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>681</v>
       </c>
@@ -31634,7 +31630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>1594</v>
       </c>
@@ -31681,7 +31677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>153</v>
       </c>
@@ -31728,7 +31724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>763</v>
       </c>
@@ -31775,7 +31771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>568</v>
       </c>
@@ -31822,7 +31818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>597</v>
       </c>
@@ -31869,7 +31865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>613</v>
       </c>
@@ -31916,7 +31912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>628</v>
       </c>
@@ -31963,7 +31959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>649</v>
       </c>
@@ -32010,7 +32006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>235</v>
       </c>
@@ -32057,7 +32053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>251</v>
       </c>
@@ -32104,7 +32100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>264</v>
       </c>
@@ -32151,7 +32147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>273</v>
       </c>
@@ -32198,7 +32194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>299</v>
       </c>
@@ -32245,7 +32241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>308</v>
       </c>
@@ -32292,7 +32288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>317</v>
       </c>
@@ -32339,7 +32335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>326</v>
       </c>
@@ -32386,7 +32382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>335</v>
       </c>
@@ -32433,7 +32429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>344</v>
       </c>
@@ -32480,7 +32476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>353</v>
       </c>
@@ -32527,7 +32523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>362</v>
       </c>
@@ -32574,7 +32570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>374</v>
       </c>
@@ -32621,7 +32617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>383</v>
       </c>
@@ -32668,7 +32664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>393</v>
       </c>
@@ -32715,7 +32711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>401</v>
       </c>
@@ -32762,7 +32758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>409</v>
       </c>
@@ -32809,7 +32805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>418</v>
       </c>
@@ -32856,7 +32852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>427</v>
       </c>
@@ -32903,7 +32899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>435</v>
       </c>
@@ -32950,7 +32946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>442</v>
       </c>
@@ -32997,7 +32993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>452</v>
       </c>
@@ -33044,7 +33040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>544</v>
       </c>
@@ -33092,13 +33088,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y559" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="24">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y559" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33557,8 +33547,8 @@
       <c r="Y5" t="s">
         <v>33</v>
       </c>
-      <c r="Z5" t="s">
-        <v>2082</v>
+      <c r="Z5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.2">
